--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562653.0744947566</v>
+        <v>562653</v>
       </c>
       <c r="R2" t="n">
-        <v>6887040.850967368</v>
+        <v>6887041</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1992-06-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562653.0744947566</v>
+        <v>562653</v>
       </c>
       <c r="R3" t="n">
-        <v>6887040.850967368</v>
+        <v>6887041</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1992-06-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1992-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562653.0744947566</v>
+        <v>562653</v>
       </c>
       <c r="R4" t="n">
-        <v>6887040.850967368</v>
+        <v>6887041</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,19 +970,9 @@
           <t>1992-06-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1992-06-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562653.0744947566</v>
+        <v>562653</v>
       </c>
       <c r="R5" t="n">
-        <v>6887040.850967368</v>
+        <v>6887041</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1131,19 +1081,9 @@
           <t>1992-06-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1992-06-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562653.0744947566</v>
+        <v>562653</v>
       </c>
       <c r="R6" t="n">
-        <v>6887040.850967368</v>
+        <v>6887041</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1257,19 +1192,9 @@
           <t>1992-06-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1992-06-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>103373</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562653.0744947566</v>
+        <v>562653</v>
       </c>
       <c r="R7" t="n">
-        <v>6887040.850967368</v>
+        <v>6887041</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1383,19 +1303,9 @@
           <t>1992-06-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1992-06-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97652</v>
+        <v>97658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105731</v>
+        <v>105740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97658</v>
+        <v>97660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105740</v>
+        <v>105752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105752</v>
+        <v>105761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97660</v>
+        <v>97661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105761</v>
+        <v>105766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97661</v>
+        <v>97688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105766</v>
+        <v>105794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97688</v>
+        <v>97694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105794</v>
+        <v>105800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97694</v>
+        <v>97701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105800</v>
+        <v>105807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97701</v>
+        <v>97705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105807</v>
+        <v>105811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97705</v>
+        <v>97712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105811</v>
+        <v>105818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97715</v>
+        <v>97720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105821</v>
+        <v>105826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82385635</v>
       </c>
       <c r="B2" t="n">
-        <v>97720</v>
+        <v>97728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82385598</v>
       </c>
       <c r="B3" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82385616</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82385617</v>
       </c>
       <c r="B5" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82385595</v>
       </c>
       <c r="B6" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82385587</v>
       </c>
       <c r="B7" t="n">
-        <v>105826</v>
+        <v>105834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19432-2025 artfynd.xlsx
+++ b/artfynd/A 19432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82385635</v>
+        <v>82385587</v>
       </c>
       <c r="B2" t="n">
-        <v>97728</v>
+        <v>106357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82385598</v>
+        <v>82385635</v>
       </c>
       <c r="B3" t="n">
-        <v>103181</v>
+        <v>98186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82385616</v>
+        <v>82385598</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>103683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82385617</v>
+        <v>82385595</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82385595</v>
+        <v>82385616</v>
       </c>
       <c r="B6" t="n">
-        <v>104127</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1230,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82385587</v>
+        <v>82385617</v>
       </c>
       <c r="B7" t="n">
-        <v>105834</v>
+        <v>101228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>674</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myskmåra</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galium triflorum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
